--- a/eval/pilot/results/20260922_064359/calificacion.xlsx
+++ b/eval/pilot/results/20260922_064359/calificacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DS_USFQ\CAPSTON\RAG\eval\pilot\results\20260922_064359\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD872B1C-3DF3-4627-B592-142B9229ED22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06C6053-994F-4250-9539-058D0C74174C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia" sheetId="5" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Contextos" sheetId="2" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Calificacion!$A$1:$R$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Contextos!$A$1:$M$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="621">
   <si>
     <t>id</t>
   </si>
@@ -105,9 +106,6 @@
   </si>
   <si>
     <t>¿Qué mitigaciones propone ATT&amp;CK para la sub-técnica T1059.001 PowerShell y en qué consiste cada una?</t>
-  </si>
-  <si>
-    <t>ATT&amp;CK lista cinco mitigaciones para T1059.001: M1038 Execution Prevention (control de aplicaciones y PowerShell Constrained Language Mode), M1045 Code Signing (política de ejecución sólo de scripts firmados), M1026 Privileged Account Management (restringir la ejecución a administradores; JEA para limitar comandos), M1049 Antivirus/Antimalware (cuarentena automática de archivos sospechosos) y M1042 Disable or Remove Feature or Program (eliminar PowerShell donde no se necesite y deshabilitar/restringir WinRM).</t>
   </si>
   <si>
     <t>-</t>
@@ -331,9 +329,6 @@
   </si>
   <si>
     <t>Según ATT&amp;CK, ¿APT29 (G0016) utiliza Mimikatz? Y en caso afirmativo, ¿qué técnicas relacionadas con tickets Kerberos implementa esa herramienta?</t>
-  </si>
-  <si>
-    <t>Sí: S0002 Mimikatz aparece en la lista de software usado por APT29 (y G0016 APT29 aparece en la lista 'Used by' de Mimikatz). Entre las técnicas de Mimikatz relacionadas con tickets Kerberos están T1550.003 Pass the Ticket, T1558.001 Golden Ticket y T1558.002 Silver Ticket.</t>
   </si>
   <si>
     <t>Sí, según ATT&amp;CK, APT29 (G0016) utiliza Mimikatz.  
@@ -4058,12 +4053,32 @@
   <si>
     <t>Respondió bien, pero con citas incorrectas</t>
   </si>
+  <si>
+    <t>recall@5</t>
+  </si>
+  <si>
+    <t>Verificar mas categorias todos, parcial, ninguna</t>
+  </si>
+  <si>
+    <t>Sí: S0002 Mimikatz aparece en la lista de software usado por APT29 (y G0016 APT29 aparece en la lista 'Used by' de Mimikatz). Entre las técnicas de Mimikatz relacionadas con tickets Kerberos están 
+T1550.003 Pass the Ticket, 
+T1558.001 Golden Ticket y 
+T1558.002 Silver Ticket.</t>
+  </si>
+  <si>
+    <t>ATT&amp;CK lista cinco mitigaciones para T1059.001: 
+M1038 Execution Prevention (control de aplicaciones y PowerShell Constrained Language Mode), 
+M1045 Code Signing (política de ejecución sólo de scripts firmados), 
+M1026 Privileged Account Management (restringir la ejecución a administradores; JEA para limitar comandos),
+ M1049 Antivirus/Antimalware (cuarentena automática de archivos sospechosos) y 
+M1042 Disable or Remove Feature or Program (eliminar PowerShell donde no se necesite y deshabilitar/restringir WinRM).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4120,6 +4135,23 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4378,10 +4410,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4491,6 +4524,9 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4522,7 +4558,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4835,75 +4872,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
     <col min="2" max="2" width="104.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
+        <v>564</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>566</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="B3" s="21" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="B4" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="C4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
         <v>568</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B5" s="21" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+    <row r="6" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>569</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B6" s="25" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
-        <v>570</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>571</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="154.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="154.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -4913,7 +4953,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q27"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="6" customWidth="1"/>
@@ -4928,10 +4969,12 @@
     <col min="11" max="11" width="25.28515625" customWidth="1"/>
     <col min="12" max="13" width="11" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="17" width="40" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" customWidth="1"/>
+    <col min="16" max="16" width="40" customWidth="1"/>
+    <col min="17" max="17" width="41.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4983,134 +5026,140 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="R1" s="41" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="99.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="44" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>620</v>
+      </c>
+      <c r="G2" s="42" t="s">
         <v>601</v>
       </c>
-      <c r="D2" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="41" t="s">
+      <c r="H2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="41" t="s">
-        <v>603</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="30" t="s">
+      <c r="K2" s="36" t="s">
         <v>24</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="36" t="s">
-        <v>25</v>
       </c>
       <c r="L2" s="37">
         <v>0</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N2" s="37" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="P2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="45"/>
+      <c r="B3" s="28" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="28" t="s">
+      <c r="C3" s="43"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="12" t="s">
+      <c r="I3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="J3" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="31" t="s">
-        <v>31</v>
-      </c>
       <c r="K3" s="31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L3" s="38">
         <v>1</v>
       </c>
       <c r="M3" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="38" t="s">
+        <v>580</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="219.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="44" t="s">
         <v>31</v>
-      </c>
-      <c r="N3" s="38" t="s">
-        <v>582</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>607</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>605</v>
-      </c>
-      <c r="Q3" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="219.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
-        <v>32</v>
       </c>
       <c r="B4" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>602</v>
-      </c>
-      <c r="D4" s="49" t="s">
+      <c r="C4" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>608</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="41" t="s">
-        <v>610</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>603</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="34" t="s">
         <v>34</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>35</v>
       </c>
       <c r="J4" s="34">
         <v>2</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L4" s="37">
         <v>1</v>
@@ -5119,88 +5168,91 @@
         <v>1</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="O4" s="8"/>
       <c r="P4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="R4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="45"/>
+      <c r="B5" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="12" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44"/>
-      <c r="B5" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12" t="s">
-        <v>39</v>
-      </c>
       <c r="I5" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="K5" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L5" s="38">
         <v>1</v>
       </c>
       <c r="M5" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N5" s="38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="O5" s="12"/>
       <c r="P5" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
-        <v>40</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="123.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>39</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="42" t="s">
         <v>601</v>
       </c>
-      <c r="D6" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="41" t="s">
+      <c r="H6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="41" t="s">
-        <v>603</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="I6" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6" s="34">
         <v>1</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L6" s="37">
         <v>2</v>
@@ -5209,88 +5261,91 @@
         <v>2</v>
       </c>
       <c r="N6" s="37" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="R6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="45"/>
+      <c r="B7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44"/>
-      <c r="B7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12" t="s">
-        <v>47</v>
-      </c>
       <c r="I7" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="39" t="s">
-        <v>31</v>
-      </c>
       <c r="K7" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L7" s="38">
         <v>2</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N7" s="38" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O7" s="12"/>
       <c r="P7" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="219.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
-        <v>48</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="219.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="44" t="s">
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="41" t="s">
-        <v>601</v>
-      </c>
-      <c r="D8" s="45" t="s">
+      <c r="C8" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="F8" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="G8" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="H8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="I8" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J8" s="34">
         <v>1</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L8" s="37">
         <v>2</v>
@@ -5299,88 +5354,91 @@
         <v>2</v>
       </c>
       <c r="N8" s="37" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="R8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="45"/>
+      <c r="B9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="43"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="12" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="44"/>
-      <c r="B9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="12" t="s">
-        <v>57</v>
-      </c>
       <c r="I9" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="39" t="s">
-        <v>31</v>
-      </c>
       <c r="K9" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L9" s="38">
         <v>1</v>
       </c>
       <c r="M9" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N9" s="38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="O9" s="12"/>
       <c r="P9" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="245.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
-        <v>58</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="233.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="44" t="s">
+        <v>57</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>619</v>
+      </c>
+      <c r="G10" s="42" t="s">
         <v>601</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="41" t="s">
+      <c r="H10" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="I10" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="33" t="s">
         <v>60</v>
-      </c>
-      <c r="G10" s="41" t="s">
-        <v>603</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="33" t="s">
-        <v>62</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -5389,88 +5447,91 @@
         <v>1</v>
       </c>
       <c r="N10" s="37" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="161.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="45"/>
+      <c r="B11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="43"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="Q10" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="161.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="44"/>
-      <c r="B11" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12" t="s">
-        <v>65</v>
-      </c>
       <c r="I11" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="39" t="s">
-        <v>31</v>
-      </c>
       <c r="K11" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L11" s="38">
         <v>0</v>
       </c>
       <c r="M11" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N11" s="38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="O11" s="12"/>
       <c r="P11" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="228.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
-        <v>66</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="228.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="44" t="s">
+        <v>64</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="41" t="s">
-        <v>601</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="H12" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="I12" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" s="34">
         <v>5</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L12" s="37">
         <v>0</v>
@@ -5479,88 +5540,91 @@
         <v>2</v>
       </c>
       <c r="N12" s="37" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="45"/>
+      <c r="B13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="43"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="Q12" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="44"/>
-      <c r="B13" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12" t="s">
-        <v>74</v>
-      </c>
       <c r="I13" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="39" t="s">
-        <v>31</v>
-      </c>
       <c r="K13" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L13" s="38">
         <v>0</v>
       </c>
       <c r="M13" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N13" s="38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="O13" s="12"/>
       <c r="P13" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
-        <v>75</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="154.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="44" t="s">
+        <v>73</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="41" t="s">
-        <v>602</v>
-      </c>
-      <c r="D14" s="49" t="s">
+      <c r="C14" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="D14" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F14" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="41" t="s">
-        <v>603</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="I14" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J14" s="34">
         <v>1</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L14" s="37">
         <v>2</v>
@@ -5569,178 +5633,184 @@
         <v>2</v>
       </c>
       <c r="N14" s="37" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="45"/>
+      <c r="B15" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="Q14" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="44"/>
-      <c r="B15" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="12" t="s">
-        <v>82</v>
-      </c>
       <c r="I15" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J15" s="39" t="s">
-        <v>31</v>
-      </c>
       <c r="K15" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L15" s="38">
         <v>0</v>
       </c>
       <c r="M15" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" s="38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="O15" s="12"/>
       <c r="P15" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="167.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
-        <v>83</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="167.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="44" t="s">
+        <v>81</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="41" t="s">
-        <v>601</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="41" t="s">
+      <c r="C16" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="42" t="s">
+        <v>607</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F16" s="41" t="s">
-        <v>609</v>
-      </c>
-      <c r="G16" s="41" t="s">
+      <c r="I16" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="33" t="s">
         <v>85</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="I16" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="33" t="s">
-        <v>87</v>
       </c>
       <c r="L16" s="37">
         <v>0</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N16" s="37" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="45"/>
+      <c r="B17" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="43"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="Q16" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
-      <c r="B17" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12" t="s">
-        <v>90</v>
-      </c>
       <c r="I17" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J17" s="39" t="s">
-        <v>31</v>
-      </c>
       <c r="K17" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L17" s="38">
         <v>0</v>
       </c>
       <c r="M17" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N17" s="38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="O17" s="12"/>
       <c r="P17" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
-        <v>91</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="44" t="s">
+        <v>89</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="41" t="s">
-        <v>602</v>
-      </c>
-      <c r="D18" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="41" t="s">
+      <c r="C18" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>609</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F18" s="41" t="s">
-        <v>611</v>
-      </c>
-      <c r="G18" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="I18" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J18" s="34">
         <v>5</v>
       </c>
       <c r="K18" s="33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L18" s="37">
         <v>0</v>
@@ -5749,416 +5819,426 @@
         <v>2</v>
       </c>
       <c r="N18" s="37" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="45"/>
+      <c r="B19" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="Q18" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="44"/>
-      <c r="B19" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="I19" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="39" t="s">
-        <v>31</v>
-      </c>
       <c r="K19" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L19" s="38">
         <v>0</v>
       </c>
       <c r="M19" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N19" s="38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="O19" s="12"/>
       <c r="P19" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="192.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
-        <v>99</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="192.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="44" t="s">
+        <v>97</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="41" t="s">
-        <v>601</v>
-      </c>
-      <c r="D20" s="47" t="s">
+      <c r="C20" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="G20" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="H20" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="41" t="s">
+      <c r="I20" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="J20" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="33" t="s">
         <v>104</v>
-      </c>
-      <c r="I20" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="J20" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="33" t="s">
-        <v>106</v>
       </c>
       <c r="L20" s="37">
         <v>2</v>
       </c>
       <c r="M20" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N20" s="37" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="44"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="45"/>
       <c r="B21" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
+        <v>27</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K21" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L21" s="38">
         <v>0</v>
       </c>
       <c r="M21" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N21" s="38" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="O21" s="12"/>
       <c r="P21" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q21" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
-        <v>109</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="101.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="44" t="s">
+        <v>107</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="41" t="s">
-        <v>602</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" s="41" t="s">
+      <c r="C22" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="I22" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="33" t="s">
         <v>111</v>
-      </c>
-      <c r="G22" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="J22" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="33" t="s">
-        <v>113</v>
       </c>
       <c r="L22" s="37">
         <v>2</v>
       </c>
       <c r="M22" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N22" s="37" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O22" s="8"/>
       <c r="P22" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" ht="248.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="44"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="248.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="45"/>
       <c r="B23" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+        <v>27</v>
+      </c>
+      <c r="C23" s="43"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J23" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K23" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L23" s="38">
         <v>0</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N23" s="38" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="O23" s="12"/>
       <c r="P23" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
-        <v>116</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="137.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="44" t="s">
+        <v>114</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="41" t="s">
-        <v>601</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="41" t="s">
+      <c r="C24" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="F24" s="41" t="s">
+      <c r="I24" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="J24" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="33" t="s">
         <v>118</v>
-      </c>
-      <c r="G24" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I24" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="J24" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="33" t="s">
-        <v>120</v>
       </c>
       <c r="L24" s="37">
         <v>2</v>
       </c>
       <c r="M24" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N24" s="37" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" ht="219.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="44"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="219.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="45"/>
       <c r="B25" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+        <v>27</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K25" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L25" s="38">
         <v>2</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N25" s="38" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O25" s="12"/>
       <c r="P25" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q25" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="43" t="s">
-        <v>123</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="44" t="s">
+        <v>121</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="41" t="s">
-        <v>601</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="41" t="s">
+      <c r="C26" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="41" t="s">
+      <c r="I26" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="J26" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="33" t="s">
         <v>125</v>
-      </c>
-      <c r="G26" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="I26" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="J26" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="33" t="s">
-        <v>127</v>
       </c>
       <c r="L26" s="37">
         <v>2</v>
       </c>
       <c r="M26" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N26" s="37" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="191.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="44"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="191.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="45"/>
       <c r="B27" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
+        <v>27</v>
+      </c>
+      <c r="C27" s="43"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
       <c r="H27" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I27" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J27" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K27" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L27" s="38">
         <v>0</v>
       </c>
       <c r="M27" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N27" s="38" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="O27" s="12"/>
       <c r="P27" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R27" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="p09"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="78">
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="D2:D3"/>
@@ -6247,6 +6327,9 @@
       <formula1>"OK,E0-corpus,E1-recuperacion,E2-generacion,E3-citas"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="R1" r:id="rId1" xr:uid="{1BD482D6-2FFF-4EBA-8B9C-BB034DE29DEB}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6264,18 +6347,18 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B2">
         <f>COUNTIFS(Calificacion!B2:B27,"RAG",Calificacion!L2:L27,"&lt;&gt;")</f>
@@ -6288,7 +6371,7 @@
     </row>
     <row r="3" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B3" s="14">
         <f>IFERROR(AVERAGEIFS(Calificacion!L2:L27,Calificacion!B2:B27,"RAG"),"")</f>
@@ -6299,50 +6382,50 @@
         <v>0.53846153846153844</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B4">
         <f>IFERROR(AVERAGEIFS(Calificacion!M2:M27,Calificacion!B2:B27,"RAG"),"")</f>
         <v>1.7142857142857142</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B5" t="str">
         <f>COUNTIFS(Calificacion!B2:B27,"RAG",Calificacion!I2:I27,"SI")&amp;" / "&amp;COUNTIFS(Calificacion!B2:B27,"RAG",Calificacion!D2:D27,"&lt;&gt;nula")</f>
         <v>6 / 9</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B8">
         <f>COUNTIFS(Calificacion!B2:B27,"RAG",Calificacion!N2:N27,"OK")</f>
@@ -6353,12 +6436,12 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B9">
         <f>COUNTIFS(Calificacion!B2:B27,"RAG",Calificacion!N2:N27,"E0-corpus")</f>
@@ -6369,12 +6452,12 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B10">
         <f>COUNTIFS(Calificacion!B2:B27,"RAG",Calificacion!N2:N27,"E1-recuperacion")</f>
@@ -6385,12 +6468,12 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B11">
         <f>COUNTIFS(Calificacion!B2:B27,"RAG",Calificacion!N2:N27,"E2-generacion")</f>
@@ -6401,12 +6484,12 @@
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B12">
         <f>COUNTIFS(Calificacion!B2:B27,"RAG",Calificacion!N2:N27,"E3-citas")</f>
@@ -6417,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -6436,36 +6519,36 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B5">
         <v>384</v>
@@ -6473,17 +6556,17 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B8">
         <v>1200</v>
@@ -6491,7 +6574,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B9">
         <v>150</v>
@@ -6499,23 +6582,23 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B11" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B12">
         <v>2616</v>
@@ -6523,7 +6606,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B13">
         <v>7241</v>
@@ -6531,7 +6614,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B14">
         <v>7241</v>
@@ -6539,7 +6622,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B15">
         <v>1779.6</v>
@@ -6547,10 +6630,10 @@
     </row>
     <row r="17" spans="1:2" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -6569,57 +6652,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C1" t="s">
         <v>584</v>
-      </c>
-      <c r="B1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C1" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C2" t="s">
         <v>588</v>
-      </c>
-      <c r="C2" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C3" t="s">
         <v>589</v>
-      </c>
-      <c r="C3" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>589</v>
-      </c>
       <c r="C4" s="15" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -6654,31 +6737,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
@@ -6689,7 +6772,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D2" s="7">
         <v>1854</v>
@@ -6711,10 +6794,10 @@
         <v>102270.3</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6722,10 +6805,10 @@
         <v>17</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D3" s="11">
         <v>162</v>
@@ -6747,21 +6830,21 @@
         <v>144912.4</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D4" s="7">
         <v>1294</v>
@@ -6783,21 +6866,21 @@
         <v>91677.8</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D5" s="11">
         <v>158</v>
@@ -6819,21 +6902,21 @@
         <v>57944.5</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D6" s="7">
         <v>1201</v>
@@ -6855,21 +6938,21 @@
         <v>68986.399999999994</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D7" s="11">
         <v>157</v>
@@ -6891,21 +6974,21 @@
         <v>46220.7</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D8" s="7">
         <v>1256</v>
@@ -6927,21 +7010,21 @@
         <v>74140.100000000006</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D9" s="11">
         <v>171</v>
@@ -6963,21 +7046,21 @@
         <v>56364.4</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D10" s="7">
         <v>1661</v>
@@ -6999,21 +7082,21 @@
         <v>108426.4</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D11" s="11">
         <v>171</v>
@@ -7035,21 +7118,21 @@
         <v>55533.9</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D12" s="7">
         <v>1714</v>
@@ -7071,21 +7154,21 @@
         <v>104349.8</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D13" s="11">
         <v>177</v>
@@ -7107,21 +7190,21 @@
         <v>37692.199999999997</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D14" s="7">
         <v>1500</v>
@@ -7143,21 +7226,21 @@
         <v>125718</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D15" s="11">
         <v>162</v>
@@ -7179,21 +7262,21 @@
         <v>74733.8</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D16" s="7">
         <v>1481</v>
@@ -7215,21 +7298,21 @@
         <v>86825</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D17" s="11">
         <v>174</v>
@@ -7251,21 +7334,21 @@
         <v>60802.1</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D18" s="7">
         <v>1444</v>
@@ -7287,21 +7370,21 @@
         <v>89928.9</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D19" s="11">
         <v>160</v>
@@ -7323,21 +7406,21 @@
         <v>96347.1</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D20" s="7">
         <v>1297</v>
@@ -7359,21 +7442,21 @@
         <v>90459.7</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D21" s="11">
         <v>157</v>
@@ -7395,21 +7478,21 @@
         <v>95539.5</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D22" s="7">
         <v>1471</v>
@@ -7431,21 +7514,21 @@
         <v>79616.899999999994</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D23" s="11">
         <v>150</v>
@@ -7467,21 +7550,21 @@
         <v>34224.1</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D24" s="7">
         <v>1430</v>
@@ -7503,21 +7586,21 @@
         <v>83160.600000000006</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D25" s="11">
         <v>155</v>
@@ -7539,21 +7622,21 @@
         <v>45225.7</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D26" s="7">
         <v>1619</v>
@@ -7575,21 +7658,21 @@
         <v>112951</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D27" s="11">
         <v>159</v>
@@ -7611,10 +7694,10 @@
         <v>44539.4</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -7649,40 +7732,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -7696,31 +7779,31 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" t="s">
         <v>141</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>142</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>144</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" t="s">
         <v>145</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>146</v>
       </c>
-      <c r="L2" t="s">
-        <v>147</v>
-      </c>
-      <c r="M2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="315" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:13" ht="315" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7734,31 +7817,31 @@
         <v>0.39219999999999999</v>
       </c>
       <c r="E3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" t="s">
         <v>149</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>150</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>152</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" t="s">
         <v>153</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>154</v>
       </c>
-      <c r="L3" t="s">
-        <v>155</v>
-      </c>
-      <c r="M3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -7772,31 +7855,31 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" t="s">
         <v>157</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>158</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" t="s">
         <v>161</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>162</v>
       </c>
-      <c r="L4" t="s">
-        <v>163</v>
-      </c>
-      <c r="M4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -7810,31 +7893,31 @@
         <v>0.25559999999999999</v>
       </c>
       <c r="E5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" t="s">
         <v>165</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>166</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J5" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>168</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="L5" t="s">
         <v>169</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>170</v>
       </c>
-      <c r="L5" t="s">
-        <v>171</v>
-      </c>
-      <c r="M5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -7848,33 +7931,33 @@
         <v>0.25</v>
       </c>
       <c r="E6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F6" t="s">
+      <c r="K6" t="s">
         <v>174</v>
       </c>
-      <c r="G6" t="s">
-        <v>151</v>
-      </c>
-      <c r="H6" t="s">
-        <v>152</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" t="s">
         <v>175</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>176</v>
-      </c>
-      <c r="L6" t="s">
-        <v>177</v>
-      </c>
-      <c r="M6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -7886,33 +7969,33 @@
         <v>0.5</v>
       </c>
       <c r="E7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H7" t="s">
         <v>179</v>
       </c>
-      <c r="F7" t="s">
+      <c r="J7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>181</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" t="s">
         <v>182</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>183</v>
-      </c>
-      <c r="L7" t="s">
-        <v>184</v>
-      </c>
-      <c r="M7" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>18</v>
@@ -7924,36 +8007,36 @@
         <v>0.5</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="I8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="L8" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="M8" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -7965,33 +8048,33 @@
         <v>0.36109999999999998</v>
       </c>
       <c r="E9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" t="s">
+        <v>141</v>
+      </c>
+      <c r="H9" t="s">
         <v>193</v>
       </c>
-      <c r="F9" t="s">
+      <c r="J9" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="K9" t="s">
         <v>195</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="L9" t="s">
         <v>196</v>
       </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
         <v>197</v>
-      </c>
-      <c r="L9" t="s">
-        <v>198</v>
-      </c>
-      <c r="M9" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
@@ -8003,33 +8086,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" t="s">
+        <v>199</v>
+      </c>
+      <c r="G10" t="s">
         <v>200</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
+        <v>150</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G10" t="s">
+      <c r="K10" t="s">
         <v>202</v>
       </c>
-      <c r="H10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="L10" t="s">
         <v>203</v>
       </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>204</v>
-      </c>
-      <c r="L10" t="s">
-        <v>205</v>
-      </c>
-      <c r="M10" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
@@ -8041,33 +8124,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F11" t="s">
+        <v>206</v>
+      </c>
+      <c r="G11" t="s">
+        <v>165</v>
+      </c>
+      <c r="H11" t="s">
         <v>207</v>
       </c>
-      <c r="F11" t="s">
+      <c r="J11" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G11" t="s">
-        <v>167</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="K11" t="s">
         <v>209</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="L11" t="s">
         <v>210</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>211</v>
-      </c>
-      <c r="L11" t="s">
-        <v>212</v>
-      </c>
-      <c r="M11" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>18</v>
@@ -8079,36 +8162,36 @@
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="I12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="K12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="3" t="s">
+      <c r="M12" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
@@ -8120,33 +8203,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E13" t="s">
+        <v>218</v>
+      </c>
+      <c r="F13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G13" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" t="s">
+        <v>193</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F13" t="s">
+      <c r="K13" t="s">
         <v>221</v>
       </c>
-      <c r="G13" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" t="s">
-        <v>195</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="L13" t="s">
         <v>222</v>
       </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>223</v>
-      </c>
-      <c r="L13" t="s">
-        <v>224</v>
-      </c>
-      <c r="M13" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
@@ -8158,33 +8241,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E14" t="s">
+        <v>224</v>
+      </c>
+      <c r="F14" t="s">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" t="s">
         <v>226</v>
       </c>
-      <c r="F14" t="s">
+      <c r="J14" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G14" t="s">
-        <v>167</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="K14" t="s">
         <v>228</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="L14" t="s">
         <v>229</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
         <v>230</v>
-      </c>
-      <c r="L14" t="s">
-        <v>231</v>
-      </c>
-      <c r="M14" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
@@ -8196,33 +8279,33 @@
         <v>0.25</v>
       </c>
       <c r="E15" t="s">
+        <v>231</v>
+      </c>
+      <c r="F15" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" t="s">
+        <v>226</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F15" t="s">
+      <c r="K15" t="s">
         <v>234</v>
       </c>
-      <c r="G15" t="s">
-        <v>143</v>
-      </c>
-      <c r="H15" t="s">
-        <v>228</v>
-      </c>
-      <c r="J15" s="2" t="s">
+      <c r="L15" t="s">
         <v>235</v>
       </c>
-      <c r="K15" t="s">
+      <c r="M15" t="s">
         <v>236</v>
-      </c>
-      <c r="L15" t="s">
-        <v>237</v>
-      </c>
-      <c r="M15" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
@@ -8234,33 +8317,33 @@
         <v>0.25</v>
       </c>
       <c r="E16" t="s">
+        <v>237</v>
+      </c>
+      <c r="F16" t="s">
+        <v>238</v>
+      </c>
+      <c r="G16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F16" t="s">
+      <c r="K16" t="s">
         <v>240</v>
       </c>
-      <c r="G16" t="s">
-        <v>143</v>
-      </c>
-      <c r="H16" t="s">
-        <v>216</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="L16" t="s">
         <v>241</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" t="s">
         <v>242</v>
-      </c>
-      <c r="L16" t="s">
-        <v>243</v>
-      </c>
-      <c r="M16" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>18</v>
@@ -8272,36 +8355,36 @@
         <v>1</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="K17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="3" t="s">
+      <c r="M17" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
@@ -8313,33 +8396,33 @@
         <v>0.66669999999999996</v>
       </c>
       <c r="E18" t="s">
+        <v>248</v>
+      </c>
+      <c r="F18" t="s">
+        <v>249</v>
+      </c>
+      <c r="G18" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" t="s">
         <v>250</v>
       </c>
-      <c r="F18" t="s">
+      <c r="J18" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G18" t="s">
-        <v>143</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="K18" t="s">
         <v>252</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="L18" t="s">
         <v>253</v>
       </c>
-      <c r="K18" t="s">
+      <c r="M18" t="s">
         <v>254</v>
-      </c>
-      <c r="L18" t="s">
-        <v>255</v>
-      </c>
-      <c r="M18" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
@@ -8351,33 +8434,33 @@
         <v>0.3</v>
       </c>
       <c r="E19" t="s">
+        <v>255</v>
+      </c>
+      <c r="F19" t="s">
+        <v>256</v>
+      </c>
+      <c r="G19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H19" t="s">
+        <v>179</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F19" t="s">
+      <c r="K19" t="s">
         <v>258</v>
       </c>
-      <c r="G19" t="s">
-        <v>159</v>
-      </c>
-      <c r="H19" t="s">
-        <v>181</v>
-      </c>
-      <c r="J19" s="2" t="s">
+      <c r="L19" t="s">
         <v>259</v>
       </c>
-      <c r="K19" t="s">
+      <c r="M19" t="s">
         <v>260</v>
-      </c>
-      <c r="L19" t="s">
-        <v>261</v>
-      </c>
-      <c r="M19" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
@@ -8389,33 +8472,33 @@
         <v>0.2576</v>
       </c>
       <c r="E20" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F20" t="s">
+      <c r="K20" t="s">
         <v>264</v>
       </c>
-      <c r="G20" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" t="s">
-        <v>152</v>
-      </c>
-      <c r="J20" s="2" t="s">
+      <c r="L20" t="s">
         <v>265</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>266</v>
-      </c>
-      <c r="L20" t="s">
-        <v>267</v>
-      </c>
-      <c r="M20" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
@@ -8427,33 +8510,33 @@
         <v>0.25</v>
       </c>
       <c r="E21" t="s">
+        <v>267</v>
+      </c>
+      <c r="F21" t="s">
+        <v>268</v>
+      </c>
+      <c r="G21" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" t="s">
         <v>269</v>
       </c>
-      <c r="F21" t="s">
+      <c r="J21" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G21" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="K21" t="s">
         <v>271</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="L21" t="s">
         <v>272</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21" t="s">
         <v>273</v>
-      </c>
-      <c r="L21" t="s">
-        <v>274</v>
-      </c>
-      <c r="M21" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
         <v>18</v>
@@ -8465,33 +8548,33 @@
         <v>0.75</v>
       </c>
       <c r="E22" t="s">
+        <v>274</v>
+      </c>
+      <c r="F22" t="s">
+        <v>275</v>
+      </c>
+      <c r="G22" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" t="s">
         <v>276</v>
       </c>
-      <c r="F22" t="s">
+      <c r="J22" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="G22" t="s">
-        <v>143</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="K22" t="s">
         <v>278</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="L22" t="s">
         <v>279</v>
       </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
         <v>280</v>
-      </c>
-      <c r="L22" t="s">
-        <v>281</v>
-      </c>
-      <c r="M22" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
@@ -8503,33 +8586,33 @@
         <v>0.55559999999999998</v>
       </c>
       <c r="E23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H23" t="s">
+        <v>281</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K23" t="s">
         <v>283</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="K23" t="s">
-        <v>285</v>
-      </c>
       <c r="L23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
@@ -8541,33 +8624,33 @@
         <v>0.44440000000000002</v>
       </c>
       <c r="E24" t="s">
+        <v>284</v>
+      </c>
+      <c r="F24" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" t="s">
         <v>286</v>
       </c>
-      <c r="F24" t="s">
+      <c r="J24" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="G24" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="K24" t="s">
         <v>288</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="L24" t="s">
         <v>289</v>
       </c>
-      <c r="K24" t="s">
+      <c r="M24" t="s">
         <v>290</v>
-      </c>
-      <c r="L24" t="s">
-        <v>291</v>
-      </c>
-      <c r="M24" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>18</v>
@@ -8579,33 +8662,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E25" t="s">
+        <v>291</v>
+      </c>
+      <c r="F25" t="s">
+        <v>292</v>
+      </c>
+      <c r="G25" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" t="s">
+        <v>150</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F25" t="s">
+      <c r="K25" t="s">
         <v>294</v>
       </c>
-      <c r="G25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H25" t="s">
-        <v>152</v>
-      </c>
-      <c r="J25" s="2" t="s">
+      <c r="L25" t="s">
         <v>295</v>
       </c>
-      <c r="K25" t="s">
+      <c r="M25" t="s">
         <v>296</v>
-      </c>
-      <c r="L25" t="s">
-        <v>297</v>
-      </c>
-      <c r="M25" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
         <v>18</v>
@@ -8617,33 +8700,33 @@
         <v>0.30259999999999998</v>
       </c>
       <c r="E26" t="s">
+        <v>297</v>
+      </c>
+      <c r="F26" t="s">
+        <v>298</v>
+      </c>
+      <c r="G26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H26" t="s">
         <v>299</v>
       </c>
-      <c r="F26" t="s">
+      <c r="J26" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G26" t="s">
-        <v>143</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="K26" t="s">
         <v>301</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="L26" t="s">
         <v>302</v>
       </c>
-      <c r="K26" t="s">
+      <c r="M26" t="s">
         <v>303</v>
-      </c>
-      <c r="L26" t="s">
-        <v>304</v>
-      </c>
-      <c r="M26" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="315" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
@@ -8655,33 +8738,33 @@
         <v>0.5</v>
       </c>
       <c r="E27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F27" t="s">
+        <v>305</v>
+      </c>
+      <c r="G27" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" t="s">
+        <v>150</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F27" t="s">
+      <c r="K27" t="s">
         <v>307</v>
       </c>
-      <c r="G27" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" t="s">
-        <v>152</v>
-      </c>
-      <c r="J27" s="2" t="s">
+      <c r="L27" t="s">
         <v>308</v>
       </c>
-      <c r="K27" t="s">
+      <c r="M27" t="s">
         <v>309</v>
-      </c>
-      <c r="L27" t="s">
-        <v>310</v>
-      </c>
-      <c r="M27" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
         <v>18</v>
@@ -8693,33 +8776,33 @@
         <v>0.5</v>
       </c>
       <c r="E28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" t="s">
         <v>157</v>
       </c>
-      <c r="F28" t="s">
-        <v>158</v>
-      </c>
-      <c r="G28" t="s">
-        <v>159</v>
-      </c>
       <c r="H28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K28" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L28" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M28" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="405" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
         <v>18</v>
@@ -8731,33 +8814,33 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="E29" t="s">
+        <v>312</v>
+      </c>
+      <c r="F29" t="s">
+        <v>313</v>
+      </c>
+      <c r="G29" t="s">
+        <v>149</v>
+      </c>
+      <c r="H29" t="s">
+        <v>150</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F29" t="s">
+      <c r="K29" t="s">
         <v>315</v>
       </c>
-      <c r="G29" t="s">
-        <v>151</v>
-      </c>
-      <c r="H29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J29" s="2" t="s">
+      <c r="L29" t="s">
         <v>316</v>
       </c>
-      <c r="K29" t="s">
+      <c r="M29" t="s">
         <v>317</v>
-      </c>
-      <c r="L29" t="s">
-        <v>318</v>
-      </c>
-      <c r="M29" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
         <v>18</v>
@@ -8769,33 +8852,33 @@
         <v>0.36670000000000003</v>
       </c>
       <c r="E30" t="s">
+        <v>318</v>
+      </c>
+      <c r="F30" t="s">
+        <v>319</v>
+      </c>
+      <c r="G30" t="s">
+        <v>157</v>
+      </c>
+      <c r="H30" t="s">
+        <v>207</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F30" t="s">
+      <c r="K30" t="s">
         <v>321</v>
       </c>
-      <c r="G30" t="s">
-        <v>159</v>
-      </c>
-      <c r="H30" t="s">
-        <v>209</v>
-      </c>
-      <c r="J30" s="2" t="s">
+      <c r="L30" t="s">
         <v>322</v>
       </c>
-      <c r="K30" t="s">
+      <c r="M30" t="s">
         <v>323</v>
-      </c>
-      <c r="L30" t="s">
-        <v>324</v>
-      </c>
-      <c r="M30" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>18</v>
@@ -8807,36 +8890,36 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="315" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>18</v>
@@ -8848,36 +8931,36 @@
         <v>1</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="I32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H32" s="4" t="s">
+      <c r="K32" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J32" s="3" t="s">
+      <c r="L32" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="M32" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>18</v>
@@ -8889,36 +8972,36 @@
         <v>0.5</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H33" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K33" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>337</v>
-      </c>
       <c r="L33" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
         <v>18</v>
@@ -8930,33 +9013,33 @@
         <v>0.47620000000000001</v>
       </c>
       <c r="E34" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F34" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G34" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H34" t="s">
+        <v>336</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="K34" t="s">
         <v>338</v>
       </c>
-      <c r="J34" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K34" t="s">
-        <v>340</v>
-      </c>
       <c r="L34" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
         <v>18</v>
@@ -8968,33 +9051,33 @@
         <v>0.41670000000000001</v>
       </c>
       <c r="E35" t="s">
+        <v>339</v>
+      </c>
+      <c r="F35" t="s">
+        <v>340</v>
+      </c>
+      <c r="G35" t="s">
         <v>341</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
+        <v>193</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G35" t="s">
+      <c r="K35" t="s">
         <v>343</v>
       </c>
-      <c r="H35" t="s">
-        <v>195</v>
-      </c>
-      <c r="J35" s="2" t="s">
+      <c r="L35" t="s">
         <v>344</v>
       </c>
-      <c r="K35" t="s">
+      <c r="M35" t="s">
         <v>345</v>
-      </c>
-      <c r="L35" t="s">
-        <v>346</v>
-      </c>
-      <c r="M35" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
         <v>18</v>
@@ -9006,33 +9089,33 @@
         <v>0.39290000000000003</v>
       </c>
       <c r="E36" t="s">
+        <v>346</v>
+      </c>
+      <c r="F36" t="s">
+        <v>347</v>
+      </c>
+      <c r="G36" t="s">
         <v>348</v>
       </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
         <v>349</v>
       </c>
-      <c r="G36" t="s">
+      <c r="J36" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="H36" t="s">
+      <c r="K36" t="s">
         <v>351</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="L36" t="s">
         <v>352</v>
       </c>
-      <c r="K36" t="s">
+      <c r="M36" t="s">
         <v>353</v>
-      </c>
-      <c r="L36" t="s">
-        <v>354</v>
-      </c>
-      <c r="M36" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
         <v>18</v>
@@ -9044,33 +9127,33 @@
         <v>0.83330000000000004</v>
       </c>
       <c r="E37" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F37" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G37" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H37" t="s">
+        <v>336</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="K37" t="s">
         <v>338</v>
       </c>
-      <c r="J37" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K37" t="s">
-        <v>340</v>
-      </c>
       <c r="L37" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
@@ -9082,33 +9165,33 @@
         <v>0.83330000000000004</v>
       </c>
       <c r="E38" t="s">
+        <v>339</v>
+      </c>
+      <c r="F38" t="s">
+        <v>340</v>
+      </c>
+      <c r="G38" t="s">
         <v>341</v>
       </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
+        <v>193</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G38" t="s">
+      <c r="K38" t="s">
         <v>343</v>
       </c>
-      <c r="H38" t="s">
-        <v>195</v>
-      </c>
-      <c r="J38" s="2" t="s">
+      <c r="L38" t="s">
         <v>344</v>
       </c>
-      <c r="K38" t="s">
+      <c r="M38" t="s">
         <v>345</v>
-      </c>
-      <c r="L38" t="s">
-        <v>346</v>
-      </c>
-      <c r="M38" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
@@ -9120,33 +9203,33 @@
         <v>0.29089999999999999</v>
       </c>
       <c r="E39" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F39" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H39" t="s">
+        <v>354</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="K39" t="s">
         <v>356</v>
       </c>
-      <c r="J39" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="K39" t="s">
-        <v>358</v>
-      </c>
       <c r="L39" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M39" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
         <v>18</v>
@@ -9158,33 +9241,33 @@
         <v>0.25</v>
       </c>
       <c r="E40" t="s">
+        <v>357</v>
+      </c>
+      <c r="F40" t="s">
+        <v>358</v>
+      </c>
+      <c r="G40" t="s">
+        <v>157</v>
+      </c>
+      <c r="H40" t="s">
+        <v>179</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="F40" t="s">
+      <c r="K40" t="s">
         <v>360</v>
       </c>
-      <c r="G40" t="s">
-        <v>159</v>
-      </c>
-      <c r="H40" t="s">
-        <v>181</v>
-      </c>
-      <c r="J40" s="2" t="s">
+      <c r="L40" t="s">
         <v>361</v>
       </c>
-      <c r="K40" t="s">
+      <c r="M40" t="s">
         <v>362</v>
-      </c>
-      <c r="L40" t="s">
-        <v>363</v>
-      </c>
-      <c r="M40" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
         <v>18</v>
@@ -9196,33 +9279,33 @@
         <v>0.25</v>
       </c>
       <c r="E41" t="s">
+        <v>363</v>
+      </c>
+      <c r="F41" t="s">
+        <v>364</v>
+      </c>
+      <c r="G41" t="s">
+        <v>141</v>
+      </c>
+      <c r="H41" t="s">
+        <v>281</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="F41" t="s">
+      <c r="K41" t="s">
         <v>366</v>
       </c>
-      <c r="G41" t="s">
-        <v>143</v>
-      </c>
-      <c r="H41" t="s">
-        <v>283</v>
-      </c>
-      <c r="J41" s="2" t="s">
+      <c r="L41" t="s">
         <v>367</v>
       </c>
-      <c r="K41" t="s">
+      <c r="M41" t="s">
         <v>368</v>
-      </c>
-      <c r="L41" t="s">
-        <v>369</v>
-      </c>
-      <c r="M41" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
         <v>18</v>
@@ -9234,33 +9317,33 @@
         <v>0.57689999999999997</v>
       </c>
       <c r="E42" t="s">
+        <v>369</v>
+      </c>
+      <c r="F42" t="s">
+        <v>370</v>
+      </c>
+      <c r="G42" t="s">
+        <v>141</v>
+      </c>
+      <c r="H42" t="s">
+        <v>207</v>
+      </c>
+      <c r="J42" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F42" t="s">
+      <c r="K42" t="s">
         <v>372</v>
       </c>
-      <c r="G42" t="s">
-        <v>143</v>
-      </c>
-      <c r="H42" t="s">
-        <v>209</v>
-      </c>
-      <c r="J42" s="2" t="s">
+      <c r="L42" t="s">
         <v>373</v>
       </c>
-      <c r="K42" t="s">
+      <c r="M42" t="s">
         <v>374</v>
-      </c>
-      <c r="L42" t="s">
-        <v>375</v>
-      </c>
-      <c r="M42" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
         <v>18</v>
@@ -9272,33 +9355,33 @@
         <v>0.5</v>
       </c>
       <c r="E43" t="s">
+        <v>184</v>
+      </c>
+      <c r="F43" t="s">
+        <v>185</v>
+      </c>
+      <c r="G43" t="s">
+        <v>165</v>
+      </c>
+      <c r="H43" t="s">
         <v>186</v>
       </c>
-      <c r="F43" t="s">
+      <c r="J43" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G43" t="s">
-        <v>167</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="K43" t="s">
         <v>188</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="L43" t="s">
         <v>189</v>
       </c>
-      <c r="K43" t="s">
+      <c r="M43" t="s">
         <v>190</v>
-      </c>
-      <c r="L43" t="s">
-        <v>191</v>
-      </c>
-      <c r="M43" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
@@ -9310,33 +9393,33 @@
         <v>0.35</v>
       </c>
       <c r="E44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F44" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G44" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H44" t="s">
+        <v>375</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="K44" t="s">
         <v>377</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="K44" t="s">
-        <v>379</v>
-      </c>
       <c r="L44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
         <v>18</v>
@@ -9348,33 +9431,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E45" t="s">
+        <v>378</v>
+      </c>
+      <c r="F45" t="s">
+        <v>370</v>
+      </c>
+      <c r="G45" t="s">
+        <v>141</v>
+      </c>
+      <c r="H45" t="s">
+        <v>186</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="K45" t="s">
         <v>380</v>
       </c>
-      <c r="F45" t="s">
-        <v>372</v>
-      </c>
-      <c r="G45" t="s">
-        <v>143</v>
-      </c>
-      <c r="H45" t="s">
-        <v>188</v>
-      </c>
-      <c r="J45" s="2" t="s">
+      <c r="L45" t="s">
         <v>381</v>
       </c>
-      <c r="K45" t="s">
+      <c r="M45" t="s">
         <v>382</v>
-      </c>
-      <c r="L45" t="s">
-        <v>383</v>
-      </c>
-      <c r="M45" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="390" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>18</v>
@@ -9386,36 +9469,36 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
         <v>18</v>
@@ -9427,33 +9510,33 @@
         <v>1</v>
       </c>
       <c r="E47" t="s">
+        <v>385</v>
+      </c>
+      <c r="F47" t="s">
+        <v>386</v>
+      </c>
+      <c r="G47" t="s">
+        <v>165</v>
+      </c>
+      <c r="H47" t="s">
+        <v>281</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F47" t="s">
+      <c r="K47" t="s">
         <v>388</v>
       </c>
-      <c r="G47" t="s">
-        <v>167</v>
-      </c>
-      <c r="H47" t="s">
-        <v>283</v>
-      </c>
-      <c r="J47" s="2" t="s">
+      <c r="L47" t="s">
         <v>389</v>
       </c>
-      <c r="K47" t="s">
+      <c r="M47" t="s">
         <v>390</v>
-      </c>
-      <c r="L47" t="s">
-        <v>391</v>
-      </c>
-      <c r="M47" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
         <v>18</v>
@@ -9465,33 +9548,33 @@
         <v>0.41670000000000001</v>
       </c>
       <c r="E48" t="s">
+        <v>391</v>
+      </c>
+      <c r="F48" t="s">
+        <v>392</v>
+      </c>
+      <c r="G48" t="s">
+        <v>141</v>
+      </c>
+      <c r="H48" t="s">
+        <v>193</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="F48" t="s">
+      <c r="K48" t="s">
         <v>394</v>
       </c>
-      <c r="G48" t="s">
-        <v>143</v>
-      </c>
-      <c r="H48" t="s">
-        <v>195</v>
-      </c>
-      <c r="J48" s="2" t="s">
+      <c r="L48" t="s">
         <v>395</v>
       </c>
-      <c r="K48" t="s">
+      <c r="M48" t="s">
         <v>396</v>
-      </c>
-      <c r="L48" t="s">
-        <v>397</v>
-      </c>
-      <c r="M48" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
@@ -9503,33 +9586,33 @@
         <v>0.39290000000000003</v>
       </c>
       <c r="E49" t="s">
+        <v>397</v>
+      </c>
+      <c r="F49" t="s">
+        <v>398</v>
+      </c>
+      <c r="G49" t="s">
+        <v>141</v>
+      </c>
+      <c r="H49" t="s">
         <v>399</v>
       </c>
-      <c r="F49" t="s">
+      <c r="J49" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="G49" t="s">
-        <v>143</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="K49" t="s">
         <v>401</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="L49" t="s">
         <v>402</v>
       </c>
-      <c r="K49" t="s">
+      <c r="M49" t="s">
         <v>403</v>
-      </c>
-      <c r="L49" t="s">
-        <v>404</v>
-      </c>
-      <c r="M49" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
         <v>18</v>
@@ -9541,33 +9624,33 @@
         <v>0.38329999999999997</v>
       </c>
       <c r="E50" t="s">
+        <v>404</v>
+      </c>
+      <c r="F50" t="s">
+        <v>405</v>
+      </c>
+      <c r="G50" t="s">
+        <v>341</v>
+      </c>
+      <c r="H50" t="s">
+        <v>214</v>
+      </c>
+      <c r="J50" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="F50" t="s">
+      <c r="K50" t="s">
         <v>407</v>
       </c>
-      <c r="G50" t="s">
-        <v>343</v>
-      </c>
-      <c r="H50" t="s">
-        <v>216</v>
-      </c>
-      <c r="J50" s="2" t="s">
+      <c r="L50" t="s">
         <v>408</v>
       </c>
-      <c r="K50" t="s">
+      <c r="M50" t="s">
         <v>409</v>
-      </c>
-      <c r="L50" t="s">
-        <v>410</v>
-      </c>
-      <c r="M50" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B51" t="s">
         <v>18</v>
@@ -9579,33 +9662,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E51" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F51" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H51" t="s">
+        <v>410</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="K51" t="s">
         <v>412</v>
       </c>
-      <c r="J51" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="K51" t="s">
-        <v>414</v>
-      </c>
       <c r="L51" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="M51" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s">
         <v>18</v>
@@ -9617,33 +9700,33 @@
         <v>0.5</v>
       </c>
       <c r="E52" t="s">
+        <v>413</v>
+      </c>
+      <c r="F52" t="s">
+        <v>414</v>
+      </c>
+      <c r="G52" t="s">
+        <v>200</v>
+      </c>
+      <c r="H52" t="s">
+        <v>349</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="F52" t="s">
+      <c r="K52" t="s">
         <v>416</v>
       </c>
-      <c r="G52" t="s">
-        <v>202</v>
-      </c>
-      <c r="H52" t="s">
-        <v>351</v>
-      </c>
-      <c r="J52" s="2" t="s">
+      <c r="L52" t="s">
         <v>417</v>
       </c>
-      <c r="K52" t="s">
+      <c r="M52" t="s">
         <v>418</v>
-      </c>
-      <c r="L52" t="s">
-        <v>419</v>
-      </c>
-      <c r="M52" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
@@ -9655,33 +9738,33 @@
         <v>0.5</v>
       </c>
       <c r="E53" t="s">
+        <v>419</v>
+      </c>
+      <c r="F53" t="s">
+        <v>420</v>
+      </c>
+      <c r="G53" t="s">
+        <v>165</v>
+      </c>
+      <c r="H53" t="s">
+        <v>179</v>
+      </c>
+      <c r="J53" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="F53" t="s">
+      <c r="K53" t="s">
         <v>422</v>
       </c>
-      <c r="G53" t="s">
-        <v>167</v>
-      </c>
-      <c r="H53" t="s">
-        <v>181</v>
-      </c>
-      <c r="J53" s="2" t="s">
+      <c r="L53" t="s">
         <v>423</v>
       </c>
-      <c r="K53" t="s">
+      <c r="M53" t="s">
         <v>424</v>
-      </c>
-      <c r="L53" t="s">
-        <v>425</v>
-      </c>
-      <c r="M53" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
@@ -9693,33 +9776,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E54" t="s">
+        <v>425</v>
+      </c>
+      <c r="F54" t="s">
+        <v>426</v>
+      </c>
+      <c r="G54" t="s">
+        <v>165</v>
+      </c>
+      <c r="H54" t="s">
         <v>427</v>
       </c>
-      <c r="F54" t="s">
+      <c r="J54" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="G54" t="s">
-        <v>167</v>
-      </c>
-      <c r="H54" t="s">
+      <c r="K54" t="s">
         <v>429</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="L54" t="s">
         <v>430</v>
       </c>
-      <c r="K54" t="s">
+      <c r="M54" t="s">
         <v>431</v>
-      </c>
-      <c r="L54" t="s">
-        <v>432</v>
-      </c>
-      <c r="M54" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
@@ -9731,33 +9814,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E55" t="s">
+        <v>432</v>
+      </c>
+      <c r="F55" t="s">
+        <v>433</v>
+      </c>
+      <c r="G55" t="s">
+        <v>141</v>
+      </c>
+      <c r="H55" t="s">
+        <v>193</v>
+      </c>
+      <c r="J55" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="F55" t="s">
+      <c r="K55" t="s">
         <v>435</v>
       </c>
-      <c r="G55" t="s">
-        <v>143</v>
-      </c>
-      <c r="H55" t="s">
-        <v>195</v>
-      </c>
-      <c r="J55" s="2" t="s">
+      <c r="L55" t="s">
         <v>436</v>
       </c>
-      <c r="K55" t="s">
+      <c r="M55" t="s">
         <v>437</v>
-      </c>
-      <c r="L55" t="s">
-        <v>438</v>
-      </c>
-      <c r="M55" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
         <v>18</v>
@@ -9769,33 +9852,33 @@
         <v>0.27139999999999997</v>
       </c>
       <c r="E56" t="s">
+        <v>438</v>
+      </c>
+      <c r="F56" t="s">
+        <v>439</v>
+      </c>
+      <c r="G56" t="s">
+        <v>200</v>
+      </c>
+      <c r="H56" t="s">
+        <v>150</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="F56" t="s">
+      <c r="K56" t="s">
         <v>441</v>
       </c>
-      <c r="G56" t="s">
-        <v>202</v>
-      </c>
-      <c r="H56" t="s">
-        <v>152</v>
-      </c>
-      <c r="J56" s="2" t="s">
+      <c r="L56" t="s">
         <v>442</v>
       </c>
-      <c r="K56" t="s">
+      <c r="M56" t="s">
         <v>443</v>
-      </c>
-      <c r="L56" t="s">
-        <v>444</v>
-      </c>
-      <c r="M56" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
@@ -9807,33 +9890,33 @@
         <v>0.5</v>
       </c>
       <c r="E57" t="s">
+        <v>444</v>
+      </c>
+      <c r="F57" t="s">
+        <v>444</v>
+      </c>
+      <c r="G57" t="s">
+        <v>348</v>
+      </c>
+      <c r="H57" t="s">
+        <v>150</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="K57" t="s">
         <v>446</v>
       </c>
-      <c r="F57" t="s">
-        <v>446</v>
-      </c>
-      <c r="G57" t="s">
-        <v>350</v>
-      </c>
-      <c r="H57" t="s">
-        <v>152</v>
-      </c>
-      <c r="J57" s="2" t="s">
+      <c r="L57" t="s">
         <v>447</v>
       </c>
-      <c r="K57" t="s">
+      <c r="M57" t="s">
         <v>448</v>
-      </c>
-      <c r="L57" t="s">
-        <v>449</v>
-      </c>
-      <c r="M57" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
@@ -9845,33 +9928,33 @@
         <v>0.5</v>
       </c>
       <c r="E58" t="s">
+        <v>449</v>
+      </c>
+      <c r="F58" t="s">
+        <v>450</v>
+      </c>
+      <c r="G58" t="s">
+        <v>149</v>
+      </c>
+      <c r="H58" t="s">
+        <v>214</v>
+      </c>
+      <c r="J58" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="F58" t="s">
+      <c r="K58" t="s">
         <v>452</v>
       </c>
-      <c r="G58" t="s">
-        <v>151</v>
-      </c>
-      <c r="H58" t="s">
-        <v>216</v>
-      </c>
-      <c r="J58" s="2" t="s">
+      <c r="L58" t="s">
         <v>453</v>
       </c>
-      <c r="K58" t="s">
+      <c r="M58" t="s">
         <v>454</v>
-      </c>
-      <c r="L58" t="s">
-        <v>455</v>
-      </c>
-      <c r="M58" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
@@ -9883,33 +9966,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E59" t="s">
+        <v>455</v>
+      </c>
+      <c r="F59" t="s">
+        <v>456</v>
+      </c>
+      <c r="G59" t="s">
+        <v>149</v>
+      </c>
+      <c r="H59" t="s">
+        <v>226</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="F59" t="s">
+      <c r="K59" t="s">
         <v>458</v>
       </c>
-      <c r="G59" t="s">
-        <v>151</v>
-      </c>
-      <c r="H59" t="s">
-        <v>228</v>
-      </c>
-      <c r="J59" s="2" t="s">
+      <c r="L59" t="s">
         <v>459</v>
       </c>
-      <c r="K59" t="s">
+      <c r="M59" t="s">
         <v>460</v>
-      </c>
-      <c r="L59" t="s">
-        <v>461</v>
-      </c>
-      <c r="M59" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
@@ -9921,33 +10004,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E60" t="s">
+        <v>461</v>
+      </c>
+      <c r="F60" t="s">
+        <v>462</v>
+      </c>
+      <c r="G60" t="s">
+        <v>141</v>
+      </c>
+      <c r="H60" t="s">
+        <v>186</v>
+      </c>
+      <c r="J60" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="F60" t="s">
+      <c r="K60" t="s">
         <v>464</v>
       </c>
-      <c r="G60" t="s">
-        <v>143</v>
-      </c>
-      <c r="H60" t="s">
-        <v>188</v>
-      </c>
-      <c r="J60" s="2" t="s">
+      <c r="L60" t="s">
         <v>465</v>
       </c>
-      <c r="K60" t="s">
+      <c r="M60" t="s">
         <v>466</v>
-      </c>
-      <c r="L60" t="s">
-        <v>467</v>
-      </c>
-      <c r="M60" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
@@ -9959,33 +10042,33 @@
         <v>0.25</v>
       </c>
       <c r="E61" t="s">
+        <v>467</v>
+      </c>
+      <c r="F61" t="s">
+        <v>468</v>
+      </c>
+      <c r="G61" t="s">
+        <v>149</v>
+      </c>
+      <c r="H61" t="s">
+        <v>226</v>
+      </c>
+      <c r="J61" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="F61" t="s">
+      <c r="K61" t="s">
         <v>470</v>
       </c>
-      <c r="G61" t="s">
-        <v>151</v>
-      </c>
-      <c r="H61" t="s">
-        <v>228</v>
-      </c>
-      <c r="J61" s="2" t="s">
+      <c r="L61" t="s">
         <v>471</v>
       </c>
-      <c r="K61" t="s">
+      <c r="M61" t="s">
         <v>472</v>
-      </c>
-      <c r="L61" t="s">
-        <v>473</v>
-      </c>
-      <c r="M61" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B62" t="s">
         <v>18</v>
@@ -9997,33 +10080,33 @@
         <v>0.5</v>
       </c>
       <c r="E62" t="s">
+        <v>473</v>
+      </c>
+      <c r="F62" t="s">
+        <v>474</v>
+      </c>
+      <c r="G62" t="s">
         <v>475</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" t="s">
+        <v>158</v>
+      </c>
+      <c r="J62" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="G62" t="s">
+      <c r="K62" t="s">
         <v>477</v>
       </c>
-      <c r="H62" t="s">
-        <v>160</v>
-      </c>
-      <c r="J62" s="2" t="s">
+      <c r="L62" t="s">
         <v>478</v>
       </c>
-      <c r="K62" t="s">
+      <c r="M62" t="s">
         <v>479</v>
-      </c>
-      <c r="L62" t="s">
-        <v>480</v>
-      </c>
-      <c r="M62" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
         <v>18</v>
@@ -10035,33 +10118,33 @@
         <v>0.5</v>
       </c>
       <c r="E63" t="s">
+        <v>480</v>
+      </c>
+      <c r="F63" t="s">
+        <v>481</v>
+      </c>
+      <c r="G63" t="s">
+        <v>141</v>
+      </c>
+      <c r="H63" t="s">
+        <v>281</v>
+      </c>
+      <c r="J63" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="F63" t="s">
+      <c r="K63" t="s">
         <v>483</v>
       </c>
-      <c r="G63" t="s">
-        <v>143</v>
-      </c>
-      <c r="H63" t="s">
-        <v>283</v>
-      </c>
-      <c r="J63" s="2" t="s">
+      <c r="L63" t="s">
         <v>484</v>
       </c>
-      <c r="K63" t="s">
+      <c r="M63" t="s">
         <v>485</v>
-      </c>
-      <c r="L63" t="s">
-        <v>486</v>
-      </c>
-      <c r="M63" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B64" t="s">
         <v>18</v>
@@ -10073,33 +10156,33 @@
         <v>0.38329999999999997</v>
       </c>
       <c r="E64" t="s">
+        <v>486</v>
+      </c>
+      <c r="F64" t="s">
+        <v>487</v>
+      </c>
+      <c r="G64" t="s">
+        <v>141</v>
+      </c>
+      <c r="H64" t="s">
+        <v>226</v>
+      </c>
+      <c r="J64" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="F64" t="s">
+      <c r="K64" t="s">
         <v>489</v>
       </c>
-      <c r="G64" t="s">
-        <v>143</v>
-      </c>
-      <c r="H64" t="s">
-        <v>228</v>
-      </c>
-      <c r="J64" s="2" t="s">
+      <c r="L64" t="s">
         <v>490</v>
       </c>
-      <c r="K64" t="s">
+      <c r="M64" t="s">
         <v>491</v>
-      </c>
-      <c r="L64" t="s">
-        <v>492</v>
-      </c>
-      <c r="M64" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B65" t="s">
         <v>18</v>
@@ -10111,33 +10194,33 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="E65" t="s">
+        <v>492</v>
+      </c>
+      <c r="F65" t="s">
+        <v>493</v>
+      </c>
+      <c r="G65" t="s">
         <v>494</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H65" t="s">
+        <v>150</v>
+      </c>
+      <c r="J65" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="G65" t="s">
+      <c r="K65" t="s">
         <v>496</v>
       </c>
-      <c r="H65" t="s">
-        <v>152</v>
-      </c>
-      <c r="J65" s="2" t="s">
+      <c r="L65" t="s">
         <v>497</v>
       </c>
-      <c r="K65" t="s">
+      <c r="M65" t="s">
         <v>498</v>
-      </c>
-      <c r="L65" t="s">
-        <v>499</v>
-      </c>
-      <c r="M65" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B66" t="s">
         <v>18</v>
@@ -10149,34 +10232,35 @@
         <v>0.29170000000000001</v>
       </c>
       <c r="E66" t="s">
+        <v>499</v>
+      </c>
+      <c r="F66" t="s">
+        <v>500</v>
+      </c>
+      <c r="G66" t="s">
+        <v>141</v>
+      </c>
+      <c r="H66" t="s">
+        <v>193</v>
+      </c>
+      <c r="J66" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="F66" t="s">
+      <c r="K66" t="s">
         <v>502</v>
       </c>
-      <c r="G66" t="s">
-        <v>143</v>
-      </c>
-      <c r="H66" t="s">
-        <v>195</v>
-      </c>
-      <c r="J66" s="2" t="s">
+      <c r="L66" t="s">
         <v>503</v>
       </c>
-      <c r="K66" t="s">
+      <c r="M66" t="s">
         <v>504</v>
-      </c>
-      <c r="L66" t="s">
-        <v>505</v>
-      </c>
-      <c r="M66" t="s">
-        <v>506</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M66" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <filterColumn colId="0">
       <filters>
+        <filter val="p01"/>
         <filter val="p09"/>
       </filters>
     </filterColumn>
